--- a/output/Human_Labeling_Target_500.xlsx
+++ b/output/Human_Labeling_Target_500.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\projects\lgai\massive_datasets\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59585323-B356-416A-879B-C74864257B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7155F589-66D8-4C9B-B18D-8461C65F0637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$501</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="1576">
   <si>
     <t>intent</t>
   </si>
@@ -3890,30 +3890,6 @@
   </si>
   <si>
     <t>what's in the news</t>
-  </si>
-  <si>
-    <t>공간이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기능이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>삭제 범위가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시단위, 분단위 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지역이 다르지만 의도가 같음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>목록 이름이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>항목 지정과 비지정 차이</t>
@@ -3924,18 +3900,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>지정범주와 자기위치범위로 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>서비스범주가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>내일과 오늘로 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>동작범위가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3948,22 +3916,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>단일의도와 다중의도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>현재, 과거 날씨 범주가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>의도가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>장소가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시간범주가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3972,18 +3928,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공간지정여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜지정여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공간명이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>what is the current temperatrue outside</t>
   </si>
   <si>
@@ -3997,14 +3941,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>다른색 변경</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜문의, 연도문의 의도다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>메일확인 범위가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4013,78 +3949,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>시간, 요일시각</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간확인 동일</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>리마인더와 지정일정 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공간범위가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>요청범위가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지정목록 여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>닉네임 지정여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜와 제목으로 삭제요청이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지정범위가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간설정여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>설정범위가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침, 오전 범주가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>내일, 요일 요청범주가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제목설정여부가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지정목록이 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>확인, 삭제 의도가 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>요청범주가 다름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>시단위, 분단위 다름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>특정 사람 / 특정 시점</t>
   </si>
   <si>
@@ -4103,21 +3971,9 @@
     <t>최신 뉴스 검색</t>
   </si>
   <si>
-    <t>커피 포트 켜기</t>
-  </si>
-  <si>
-    <t>조명 끄기</t>
-  </si>
-  <si>
     <t>특정 이벤트 삭제</t>
   </si>
   <si>
-    <t>특정 도시 시간 안내</t>
-  </si>
-  <si>
-    <t>조명 세기 올리기</t>
-  </si>
-  <si>
     <t>조명 세기 올리기 / 조명 켜기</t>
   </si>
   <si>
@@ -4130,60 +3986,15 @@
     <t>검색 / 다음곡</t>
   </si>
   <si>
-    <t>친구 / 일정 추가</t>
-  </si>
-  <si>
-    <t>달력에 이벤트 추가</t>
-  </si>
-  <si>
-    <t>전체 / 선택</t>
-  </si>
-  <si>
-    <t>특정 목록에 항목 추가</t>
-  </si>
-  <si>
-    <t>특정 위치 날씨</t>
-  </si>
-  <si>
-    <t>특정일 이벤트</t>
-  </si>
-  <si>
-    <t>일정 알림 등록</t>
-  </si>
-  <si>
-    <t>이벤트 삭제 / 캘린더 삭제</t>
-  </si>
-  <si>
-    <t>내일 / 오늘 오후</t>
-  </si>
-  <si>
     <t>메일 로드 / 메일 추가</t>
   </si>
   <si>
-    <t>이벤트 삭제 / 목록 삭제</t>
-  </si>
-  <si>
     <t>일부 / 전체</t>
   </si>
   <si>
     <t>특정 음악 듣기</t>
   </si>
   <si>
-    <t>특정 위치 시간</t>
-  </si>
-  <si>
-    <t>일정 확인</t>
-  </si>
-  <si>
-    <t>일정 확인 / 등록</t>
-  </si>
-  <si>
-    <t>루틴 / 현재</t>
-  </si>
-  <si>
-    <t>특정 조명 색으로 변경</t>
-  </si>
-  <si>
     <t xml:space="preserve">특정 재생목록에서 노래 검색 후 재생 </t>
   </si>
   <si>
@@ -4193,72 +4004,36 @@
     <t>특정 시간 알림 설정</t>
   </si>
   <si>
-    <t>특정위치 시간</t>
-  </si>
-  <si>
     <t>일정 목록 / 특정 일정 상세</t>
   </si>
   <si>
-    <t>일정 알림 등록 / 특정 일정 상세</t>
-  </si>
-  <si>
-    <t xml:space="preserve">목록 확인 </t>
-  </si>
-  <si>
     <t>동작 / 초기화</t>
   </si>
   <si>
-    <t>목록 리스트 / 목록 생성</t>
-  </si>
-  <si>
-    <t>목록 리스트 / 목록 상세</t>
-  </si>
-  <si>
     <t>목록 삭제 / 특정 항목 삭제</t>
   </si>
   <si>
-    <t>다용도실 / 화장실</t>
-  </si>
-  <si>
     <t>다음주 화요일 / 내일</t>
   </si>
   <si>
-    <t>오늘 / 다음 수요일</t>
-  </si>
-  <si>
     <t>특정 인원 / 전체</t>
   </si>
   <si>
     <t>목록 지우기 / 아이템 지우기</t>
   </si>
   <si>
-    <t>목록에 일부 항목 추가</t>
-  </si>
-  <si>
-    <t>일정 알림 등록 / 일정 등록</t>
-  </si>
-  <si>
     <t>특정 인원 새 영화</t>
   </si>
   <si>
-    <t>오늘 / 다음 전체</t>
-  </si>
-  <si>
     <t>특정 시점 알림 설정</t>
   </si>
   <si>
     <t>특정 위치</t>
   </si>
   <si>
-    <t>특정일 이벤트 알림</t>
-  </si>
-  <si>
     <t>일정 알림 삭제 / 미팅 삭제</t>
   </si>
   <si>
-    <t>화장실 / 아들방</t>
-  </si>
-  <si>
     <t>특정 이벤트 / 목록 전체</t>
   </si>
   <si>
@@ -4274,16 +4049,7 @@
     <t>특정 조건에 따른 노래 재생</t>
   </si>
   <si>
-    <t>이번주 / 하루</t>
-  </si>
-  <si>
-    <t>확인 / 삭제</t>
-  </si>
-  <si>
     <t>조명 세기 / 켜기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">목록 상세 / 목록 리스트 </t>
   </si>
   <si>
     <t>일정 확인 / 리마인더 확인</t>
@@ -4302,32 +4068,19 @@
     <t>특정 가수 노래 재생</t>
   </si>
   <si>
-    <t>목록 상세 / 목록 리스트</t>
-  </si>
-  <si>
     <t>목록 특정 항목 삭제</t>
   </si>
   <si>
     <t>색 변경 / 밝기 변경</t>
   </si>
   <si>
-    <t>조명 끄기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>이메일 주소 추가</t>
   </si>
   <si>
     <t>단어 정의 검색</t>
   </si>
   <si>
-    <t>요리법 / 조리 시간</t>
-  </si>
-  <si>
     <t>캘린더 리마인더 설정</t>
-  </si>
-  <si>
-    <t>장소 / 날짜</t>
   </si>
   <si>
     <t>레시피 검색</t>
@@ -4340,33 +4093,18 @@
     <t>특정 색 / 밝기 대비</t>
   </si>
   <si>
-    <t>내일 / 오늘</t>
-  </si>
-  <si>
     <t>목록 읽기 / 목록 추가</t>
   </si>
   <si>
-    <t>날짜 / 시간</t>
-  </si>
-  <si>
-    <t>목록 확인 / 목록 수</t>
-  </si>
-  <si>
     <t>특정 노래 / 장르 노래</t>
   </si>
   <si>
-    <t>반복 알림 / 일정 수정</t>
-  </si>
-  <si>
     <t>다가오는 일정 확인</t>
   </si>
   <si>
     <t>이벤트 리마인더 / 다가오는 일정</t>
   </si>
   <si>
-    <t>커피 머신 설정</t>
-  </si>
-  <si>
     <t>목록 확인</t>
   </si>
   <si>
@@ -4382,165 +4120,826 @@
     <t>특정 시간 알람 설정</t>
   </si>
   <si>
-    <t>현재 시간</t>
+    <t>색 변경 / 특정 색 변경</t>
+  </si>
+  <si>
+    <t>이메일 답장</t>
+  </si>
+  <si>
+    <t>전체 이메일 / 특정 발신자</t>
+  </si>
+  <si>
+    <t>농담 요청</t>
+  </si>
+  <si>
+    <t>특정 노래 재생</t>
+  </si>
+  <si>
+    <t>게임 종류</t>
+  </si>
+  <si>
+    <t>오늘 / 내일 특정 시간</t>
+  </si>
+  <si>
+    <t>특정 장소 / 전체 조명</t>
+  </si>
+  <si>
+    <t>특정 이벤트 시간 / 오늘 이벤트</t>
+  </si>
+  <si>
+    <t>특정 발신자 / 특정 내용</t>
+  </si>
+  <si>
+    <t>알람 확인</t>
+  </si>
+  <si>
+    <t>이벤트 추가 / 다가오는 일정</t>
+  </si>
+  <si>
+    <t>특정일 미팅 확인</t>
+  </si>
+  <si>
+    <t>특정인에게 이메일 보내기</t>
+  </si>
+  <si>
+    <t>아들방 / 거실</t>
+  </si>
+  <si>
+    <t>다음 / 특정 날짜</t>
+  </si>
+  <si>
+    <t>조명 밝기 올리기</t>
+  </si>
+  <si>
+    <t>목록 조회 / 항목 추가</t>
+  </si>
+  <si>
+    <t>오늘 / 이번주</t>
+  </si>
+  <si>
+    <t>새 이메일 확인</t>
+  </si>
+  <si>
+    <t>특정 이벤트 / 전체</t>
+  </si>
+  <si>
+    <t>오늘 일정 / 다음 계획</t>
+  </si>
+  <si>
+    <t>특정 이벤트 삭제 / 미팅 취소</t>
+  </si>
+  <si>
+    <t>특정인에게 이메일</t>
+  </si>
+  <si>
+    <t>특정 시간대 / 하루 전체</t>
+  </si>
+  <si>
+    <t>노래 재생</t>
+  </si>
+  <si>
+    <t>알람 삭제</t>
+  </si>
+  <si>
+    <t>특정 발신자 / 최신 이메일</t>
+  </si>
+  <si>
+    <t>특정 시간 리마인더</t>
+  </si>
+  <si>
+    <t>목록 보기 / 읽기</t>
+  </si>
+  <si>
+    <t>알람 삭제 / 알람 끄기</t>
+  </si>
+  <si>
+    <t>달력 추가 / 리마인더</t>
+  </si>
+  <si>
+    <t>팀 전체 / 특정인</t>
+  </si>
+  <si>
+    <t>발라드 / 록</t>
+  </si>
+  <si>
+    <t>환율 안내</t>
+  </si>
+  <si>
+    <t>요일확인의도 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요일확인 / 날짜 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜확인의도 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜확인 / 요일확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간확인 / 날짜확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜확인 / 시간확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남은시간확인 / 시간확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜확인 / 요일확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번주 날씨문의 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 날씨문의 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재위치날씨 / 특정위치 날씨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정위치 날씨문의 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 날씨 / 오늘 날씨</t>
+  </si>
+  <si>
+    <t>내일 날씨 / 비올 날씨</t>
+  </si>
+  <si>
+    <t>오늘 날씨 / 특정위치 날씨</t>
+  </si>
+  <si>
+    <t>오늘 날씨 / 내일 날씨</t>
+  </si>
+  <si>
+    <t>오늘 날씨 / 과거 날씨</t>
+  </si>
+  <si>
+    <t>과거 날씨 / 오늘 특정위치 날씨</t>
+  </si>
+  <si>
+    <t>이번주 날씨 / 특정위치 날씨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정위치 날씨 / 이번주 날씨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 날씨 / 오늘 날씨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 날씨문의동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 날씨문의동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘날씨문의동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정위치날씨 / 날씨문의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정위치날씨 / 오늘날씨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날씨문의 / 기온문의</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>색 변경 / 특정 색 변경</t>
-  </si>
-  <si>
-    <t>이메일 답장</t>
-  </si>
-  <si>
-    <t>전체 이메일 / 특정 발신자</t>
-  </si>
-  <si>
-    <t>농담 요청</t>
-  </si>
-  <si>
-    <t>특정 노래 재생</t>
-  </si>
-  <si>
-    <t>게임 종류</t>
-  </si>
-  <si>
-    <t>오늘 / 내일 특정 시간</t>
-  </si>
-  <si>
-    <t>특정 장소 / 전체 조명</t>
-  </si>
-  <si>
-    <t>날씨</t>
+    <t>특정지역 시간확인의도 동일</t>
+  </si>
+  <si>
+    <t>커피요청동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명끄기동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침실 / 거실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명 밝기 올리기 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동일공간 조명끄기동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>청소기동작동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동일공간 조명색상 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명 색상 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명색상 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이방 / 거실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단일제어의도 / 다중제어의도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명끄끼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거실 / 사무실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명 밝기 내리기 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 / 머리 맡 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간지정없음 / 머리맡 공간지정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거실 / 주방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현관 / 거실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간, 조명색상이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 / 거실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간지정없음 / 다용도실 공간지정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>청소기동작 / 청소기사용문의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 닉네임지정 / 기기명지정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간지정없음 / 거실 공간지정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피설정요청동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사무실공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방 / 머리맡 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현관 / 주방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명 동일 색상 제어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현관 공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거실 / 아들방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피포트겨기동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>베란다 공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피요청 / 매일커피요청(루틴)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청 색상 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다용도실 / 화장실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침실 / 안방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이닝룸 / 침실 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화장실 / 아들방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침실 / 주방 공간이 다름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간지정없음 / 주방 공간지정</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>특정 이벤트 시간 / 오늘 이벤트</t>
-  </si>
-  <si>
-    <t>특정 발신자 / 특정 내용</t>
-  </si>
-  <si>
-    <t>커피만들기</t>
+    <t>공간지정없음 / 현관 공간지정</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>커피 만들기</t>
-  </si>
-  <si>
-    <t>알람 확인</t>
-  </si>
-  <si>
-    <t>할일 / 일정</t>
-  </si>
-  <si>
-    <t>이벤트 추가 / 다가오는 일정</t>
-  </si>
-  <si>
-    <t>특정일 미팅 확인</t>
-  </si>
-  <si>
-    <t>특정인에게 이메일 보내기</t>
-  </si>
-  <si>
-    <t>아들방 / 거실</t>
-  </si>
-  <si>
-    <t>다음 / 특정 날짜</t>
-  </si>
-  <si>
-    <t>조명 밝기 올리기</t>
-  </si>
-  <si>
-    <t>목록 조회 / 항목 추가</t>
-  </si>
-  <si>
-    <t>오늘 / 이번주</t>
-  </si>
-  <si>
-    <t>오늘 다음 / 월요일</t>
-  </si>
-  <si>
-    <t>새 이메일 확인</t>
-  </si>
-  <si>
-    <t>할일 목록 / 전체 목록</t>
-  </si>
-  <si>
-    <t>특정 이벤트 / 전체</t>
-  </si>
-  <si>
-    <t>오늘 일정 / 다음 계획</t>
-  </si>
-  <si>
-    <t>날짜 / 요일</t>
-  </si>
-  <si>
-    <t>특정 이벤트 삭제 / 미팅 취소</t>
-  </si>
-  <si>
-    <t>전원 끄기</t>
-  </si>
-  <si>
-    <t>특정인에게 이메일</t>
-  </si>
-  <si>
-    <t>특정 시간대 / 하루 전체</t>
-  </si>
-  <si>
-    <t>이벤트 생성 / 리마인더</t>
-  </si>
-  <si>
-    <t>생일 달력 등록</t>
-  </si>
-  <si>
-    <t>특정 위치 / 현재 위치</t>
-  </si>
-  <si>
-    <t>조명 색 변경</t>
-  </si>
-  <si>
-    <t>노래 재생</t>
-  </si>
-  <si>
-    <t>달력 미팅 추가</t>
-  </si>
-  <si>
-    <t>알람 삭제</t>
-  </si>
-  <si>
-    <t>특정 발신자 / 최신 이메일</t>
-  </si>
-  <si>
-    <t>특정 시간 리마인더</t>
-  </si>
-  <si>
-    <t>오늘 날씨 활동 관련</t>
+    <t>특정시간커피설정(루틴)/커피 머신 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방 공간지정 / 공간지정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피요청동일</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>목록 보기 / 읽기</t>
-  </si>
-  <si>
-    <t>알람 삭제 / 알람 끄기</t>
-  </si>
-  <si>
-    <t>오늘/ 오후</t>
+    <t>기기명제어 / 제어요청된기기명없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침실 공간지정, 색상지정 / 색변경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 리마인드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 일정 삭제동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 일정 삭제동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 일정 삭제 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 추가 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든일정 / 특정일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 일정 삭제 / 특정 일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 삭제 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 일정 리마인드 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 일정 리마인더 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">특정일정 조회 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 설정 / 일정 조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정 삭제 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더 설정 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더조회 / 일정 조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정추가설정동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드설정동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘일정조회 / 이번주 일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>make sure there is no events on my calendar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정추가 / 리마인더추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더추가 / 일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 / 내일 일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더조회 / 일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든일정삭제 / 특정일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정추가동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜일정삭제 / 일정제목으로 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음일정저회 / 모든일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정추가 / 리마인더설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정삭제 / 모든일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든일정삭제동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요일일정설정 / 내일일정설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목설정 / 제목설정없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메주특정요일리마인더설정동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체일정조회 / 특정일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 조회갯수지정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 추가 / 반복일정 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정추가 / 반복일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 특정일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정반복리마인드동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 전 리마인드동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간 전 리마인드동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 기간일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 특정일정상세문의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 리마인더 등록 / 특정 일정 상세</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 일정삭제 / 특정기간 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정삭제  /특정기간일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기간일정삭제 / 특정일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드설정 / 일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 다음 일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인더설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정기간일정삭제 / 모든일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 이벤트 상세조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번주 / 하루 일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정상세조회/특정일정조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리마인드설정 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 / 오늘 일정삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정일정조회 / 특정일정상세조회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음일정 / 특정일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 추가 / 리마인더</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정삭제 / 특정일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드 등록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정등록 / 일정반복등록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정등록동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정조회 / 특정일정조회</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>달력 추가 / 리마인더</t>
-  </si>
-  <si>
-    <t>팀 전체 / 특정인</t>
-  </si>
-  <si>
-    <t>발라드 / 록</t>
-  </si>
-  <si>
-    <t>조명 어둡게</t>
-  </si>
-  <si>
-    <t>환율 안내</t>
+    <t>목록 모두 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 목록 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목 지정 / 제목 비지정 목록 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 확인 / 목록 개수 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 목록 삭제 / 특정 목록 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 목록 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 요청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 삭제 / 목록 문구삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 항목 삭제 / 목록 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 목록 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 항목 삭제 / 목록 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 목록 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정목록에 특정항목 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 확인 / 목록 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 항목 확인 / 목록 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>캘린더에서 일정들 지워</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 일정삭제 / 특정 일정 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 일정(일정들) 삭제동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시단위 / 분단위까지 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시단위 설정 동일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리마인드설정 / 알람설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4620,7 +5019,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -4650,6 +5049,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5057,6 +5462,9 @@
       <c r="I3" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J3" s="3" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -5086,6 +5494,9 @@
       <c r="I4" s="6" t="b">
         <v>1</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -5115,6 +5526,9 @@
       <c r="I5" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J5" s="3" t="s">
+        <v>1430</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -5145,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>1289</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -5177,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1290</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
@@ -5191,7 +5605,7 @@
         <v>6918</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>621</v>
+        <v>1569</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>622</v>
@@ -5206,10 +5620,10 @@
         <v>721</v>
       </c>
       <c r="I8" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>1291</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
@@ -5238,10 +5652,10 @@
         <v>777</v>
       </c>
       <c r="I9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>1291</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -5272,6 +5686,9 @@
       <c r="I10" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J10" s="3" t="s">
+        <v>1475</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -5302,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1292</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -5333,6 +5750,9 @@
       <c r="I12" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J12" s="3" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -5363,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1293</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -5394,6 +5814,9 @@
       <c r="I14" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J14" s="3" t="s">
+        <v>1426</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -5452,8 +5875,11 @@
       <c r="I16" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J16" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -5481,8 +5907,11 @@
       <c r="I17" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+      <c r="J17" s="3" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -5510,8 +5939,11 @@
       <c r="I18" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J18" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -5539,8 +5971,11 @@
       <c r="I19" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J19" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -5568,8 +6003,11 @@
       <c r="I20" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J20" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -5597,8 +6035,11 @@
       <c r="I21" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J21" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>176</v>
       </c>
@@ -5626,8 +6067,11 @@
       <c r="I22" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J22" s="3" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>137</v>
       </c>
@@ -5655,8 +6099,11 @@
       <c r="I23" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+      <c r="J23" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>377</v>
       </c>
@@ -5685,7 +6132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -5713,8 +6160,11 @@
       <c r="I25" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J25" s="3" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -5743,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>111</v>
       </c>
@@ -5771,8 +6221,11 @@
       <c r="I27" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J27" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -5800,8 +6253,11 @@
       <c r="I28" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J28" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>116</v>
       </c>
@@ -5829,8 +6285,11 @@
       <c r="I29" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J29" s="3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -5859,7 +6318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>266</v>
       </c>
@@ -5888,7 +6347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -5915,6 +6374,9 @@
       </c>
       <c r="I32" s="5" t="b">
         <v>1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>1422</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
@@ -5946,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1294</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
@@ -5978,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
@@ -6009,6 +6471,9 @@
       <c r="I35" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J35" s="3" t="s">
+        <v>1404</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -6039,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>1291</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -6071,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
@@ -6102,6 +6567,9 @@
       <c r="I38" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J38" s="3" t="s">
+        <v>1479</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
@@ -6131,6 +6599,9 @@
       <c r="I39" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J39" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="40" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
@@ -6160,6 +6631,9 @@
       <c r="I40" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J40" s="3" t="s">
+        <v>1564</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
@@ -6189,6 +6663,9 @@
       <c r="I41" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J41" s="11" t="s">
+        <v>1552</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
@@ -6218,6 +6695,9 @@
       <c r="I42" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J42" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
@@ -6248,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>1297</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
@@ -6280,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
@@ -6312,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>1299</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
@@ -6344,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -6376,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>1292</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
@@ -6405,7 +6885,10 @@
         <v>344</v>
       </c>
       <c r="I48" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>1408</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
@@ -6437,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
@@ -6468,6 +6951,9 @@
       <c r="I50" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J50" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
@@ -6497,6 +6983,9 @@
       <c r="I51" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J51" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="52" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
@@ -6526,6 +7015,9 @@
       <c r="I52" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J52" s="3" t="s">
+        <v>1479</v>
+      </c>
     </row>
     <row r="53" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
@@ -6555,6 +7047,9 @@
       <c r="I53" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J53" s="3" t="s">
+        <v>1427</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
@@ -6584,6 +7079,9 @@
       <c r="I54" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J54" s="3" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
@@ -6611,10 +7109,10 @@
         <v>642</v>
       </c>
       <c r="I55" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>1291</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
@@ -6646,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -6677,6 +7175,9 @@
       <c r="I57" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J57" s="3" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
@@ -6706,6 +7207,9 @@
       <c r="I58" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J58" s="3" t="s">
+        <v>1477</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
@@ -6764,6 +7268,9 @@
       <c r="I60" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J60" s="3" t="s">
+        <v>1477</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
@@ -6822,6 +7329,9 @@
       <c r="I62" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J62" s="3" t="s">
+        <v>1564</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
@@ -6852,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>1291</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -6884,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>1289</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -6915,8 +7425,8 @@
       <c r="I65" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>1291</v>
+      <c r="J65" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
@@ -6947,6 +7457,9 @@
       <c r="I66" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J66" s="3" t="s">
+        <v>1477</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
@@ -7005,8 +7518,8 @@
       <c r="I68" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="s">
-        <v>1291</v>
+      <c r="J68" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7038,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>1303</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
@@ -7067,10 +7580,10 @@
         <v>853</v>
       </c>
       <c r="I70" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>1291</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7102,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>1304</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
@@ -7134,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>1305</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
@@ -7165,6 +7678,9 @@
       <c r="I73" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J73" s="3" t="s">
+        <v>1434</v>
+      </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
@@ -7195,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>1306</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7226,6 +7742,9 @@
       <c r="I75" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J75" s="3" t="s">
+        <v>1482</v>
+      </c>
     </row>
     <row r="76" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
@@ -7255,6 +7774,9 @@
       <c r="I76" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J76" s="3" t="s">
+        <v>1483</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
@@ -7314,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>1291</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
@@ -7345,6 +7867,9 @@
       <c r="I79" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J79" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
@@ -7374,6 +7899,9 @@
       <c r="I80" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J80" s="3" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="81" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
@@ -7401,7 +7929,10 @@
         <v>322</v>
       </c>
       <c r="I81" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
@@ -7432,6 +7963,9 @@
       <c r="I82" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J82" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
@@ -7461,6 +7995,9 @@
       <c r="I83" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J83" s="3" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
@@ -7491,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>1305</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7522,6 +8059,9 @@
       <c r="I85" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J85" s="3" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
@@ -7552,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>1305</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
@@ -7583,8 +8123,8 @@
       <c r="I87" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>1305</v>
+      <c r="J87" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
@@ -7645,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7677,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>1305</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
@@ -7708,6 +8248,9 @@
       <c r="I91" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J91" s="3" t="s">
+        <v>1436</v>
+      </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
@@ -7737,6 +8280,9 @@
       <c r="I92" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J92" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="93" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
@@ -7767,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
@@ -7798,6 +8344,9 @@
       <c r="I94" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J94" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
@@ -7828,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>1309</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7857,10 +8406,10 @@
         <v>196</v>
       </c>
       <c r="I96" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>1310</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
@@ -7889,7 +8438,10 @@
         <v>1022</v>
       </c>
       <c r="I97" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>1438</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -7921,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>1305</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
@@ -7953,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>1311</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
@@ -7984,6 +8536,9 @@
       <c r="I100" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J100" s="3" t="s">
+        <v>1397</v>
+      </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
@@ -8013,6 +8568,9 @@
       <c r="I101" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J101" s="12" t="s">
+        <v>1553</v>
+      </c>
     </row>
     <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
@@ -8069,7 +8627,10 @@
         <v>1022</v>
       </c>
       <c r="I103" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>1438</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -8098,10 +8659,10 @@
         <v>131</v>
       </c>
       <c r="I104" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>1305</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
@@ -8133,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>1291</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
@@ -8164,6 +8725,9 @@
       <c r="I106" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J106" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="107" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
@@ -8193,6 +8757,9 @@
       <c r="I107" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J107" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
@@ -8222,6 +8789,9 @@
       <c r="I108" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J108" s="3" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
@@ -8252,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>1289</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
@@ -8284,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8316,7 +8886,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>1315</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8348,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>1316</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
@@ -8409,7 +8979,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>1317</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
@@ -8440,6 +9010,9 @@
       <c r="I115" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J115" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
@@ -8470,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>1309</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8502,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
@@ -8533,6 +9106,9 @@
       <c r="I118" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J118" s="12" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="119" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
@@ -8562,6 +9138,9 @@
       <c r="I119" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J119" s="3" t="s">
+        <v>1397</v>
+      </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
@@ -8591,6 +9170,9 @@
       <c r="I120" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J120" s="3" t="s">
+        <v>1573</v>
+      </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
@@ -8649,6 +9231,9 @@
       <c r="I122" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J122" s="3" t="s">
+        <v>1487</v>
+      </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
@@ -8679,7 +9264,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8708,10 +9293,10 @@
         <v>1050</v>
       </c>
       <c r="I124" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>1320</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8742,8 +9327,8 @@
       <c r="I125" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J125" s="3" t="s">
-        <v>1291</v>
+      <c r="J125" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -8774,6 +9359,9 @@
       <c r="I126" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J126" s="3" t="s">
+        <v>1488</v>
+      </c>
     </row>
     <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
@@ -8804,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>1321</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
@@ -8836,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>1322</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -8865,7 +9453,10 @@
         <v>208</v>
       </c>
       <c r="I129" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>1490</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
@@ -8954,6 +9545,9 @@
       <c r="I132" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J132" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="133" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
@@ -8983,6 +9577,9 @@
       <c r="I133" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J133" s="3" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="134" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
@@ -9012,6 +9609,9 @@
       <c r="I134" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J134" s="3" t="s">
+        <v>1403</v>
+      </c>
     </row>
     <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
@@ -9042,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1323</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9073,6 +9673,9 @@
       <c r="I136" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J136" s="3" t="s">
+        <v>1573</v>
+      </c>
     </row>
     <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
@@ -9102,6 +9705,9 @@
       <c r="I137" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J137" s="3" t="s">
+        <v>1416</v>
+      </c>
     </row>
     <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
@@ -9131,6 +9737,9 @@
       <c r="I138" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J138" s="3" t="s">
+        <v>1491</v>
+      </c>
     </row>
     <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
@@ -9158,7 +9767,10 @@
         <v>1090</v>
       </c>
       <c r="I139" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>1405</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9190,7 +9802,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
@@ -9221,6 +9833,9 @@
       <c r="I141" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J141" s="12" t="s">
+        <v>1558</v>
+      </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
@@ -9250,8 +9865,8 @@
       <c r="I142" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J142" s="3" t="s">
-        <v>1305</v>
+      <c r="J142" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
@@ -9282,6 +9897,9 @@
       <c r="I143" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J143" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
@@ -9312,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1309</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
@@ -9343,6 +9961,9 @@
       <c r="I145" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J145" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
@@ -9372,6 +9993,9 @@
       <c r="I146" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J146" s="3" t="s">
+        <v>1491</v>
+      </c>
     </row>
     <row r="147" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
@@ -9401,6 +10025,9 @@
       <c r="I147" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J147" s="3" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="148" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
@@ -9431,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>1324</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9448,7 +10075,7 @@
         <v>831</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>832</v>
+        <v>1494</v>
       </c>
       <c r="F149" s="3">
         <v>8666</v>
@@ -9461,6 +10088,9 @@
       </c>
       <c r="I149" s="5" t="b">
         <v>0</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>1493</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
@@ -9492,7 +10122,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>1309</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
@@ -9523,8 +10153,8 @@
       <c r="I151" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="s">
-        <v>1305</v>
+      <c r="J151" s="9" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9556,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1305</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9585,7 +10215,10 @@
         <v>424</v>
       </c>
       <c r="I153" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>1422</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -9616,6 +10249,9 @@
       <c r="I154" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J154" s="3" t="s">
+        <v>1496</v>
+      </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
@@ -9646,7 +10282,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>1325</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
@@ -9678,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>1291</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9709,6 +10345,9 @@
       <c r="I157" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J157" s="3" t="s">
+        <v>1493</v>
+      </c>
     </row>
     <row r="158" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
@@ -9739,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>1305</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
@@ -9771,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1326</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
@@ -9803,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>1291</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9834,6 +10473,9 @@
       <c r="I161" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J161" s="3" t="s">
+        <v>1497</v>
+      </c>
     </row>
     <row r="162" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
@@ -9849,7 +10491,7 @@
         <v>335</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1312</v>
+        <v>1298</v>
       </c>
       <c r="F162" s="3">
         <v>2178</v>
@@ -9862,6 +10504,9 @@
       </c>
       <c r="I162" s="5" t="b">
         <v>1</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>1417</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9892,6 +10537,9 @@
       <c r="I163" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J163" s="3" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="164" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
@@ -9922,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>1324</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9951,7 +10599,10 @@
         <v>851</v>
       </c>
       <c r="I165" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>1493</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -9982,6 +10633,9 @@
       <c r="I166" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J166" s="3" t="s">
+        <v>1499</v>
+      </c>
     </row>
     <row r="167" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
@@ -10067,10 +10721,10 @@
         <v>620</v>
       </c>
       <c r="I169" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>1324</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
@@ -10102,7 +10756,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10131,7 +10785,10 @@
         <v>509</v>
       </c>
       <c r="I171" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>1412</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
@@ -10162,6 +10819,9 @@
       <c r="I172" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J172" s="3" t="s">
+        <v>1501</v>
+      </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
@@ -10189,10 +10849,10 @@
         <v>684</v>
       </c>
       <c r="I173" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>1294</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10223,6 +10883,9 @@
       <c r="I174" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J174" s="3" t="s">
+        <v>1495</v>
+      </c>
     </row>
     <row r="175" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
@@ -10253,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>1291</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10282,7 +10945,10 @@
         <v>682</v>
       </c>
       <c r="I176" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>1410</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
@@ -10342,6 +11008,9 @@
       <c r="I178" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J178" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="179" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
@@ -10369,7 +11038,10 @@
         <v>322</v>
       </c>
       <c r="I179" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>1413</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10400,6 +11072,9 @@
       <c r="I180" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J180" s="3" t="s">
+        <v>1562</v>
+      </c>
     </row>
     <row r="181" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
@@ -10429,6 +11104,9 @@
       <c r="I181" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J181" s="3" t="s">
+        <v>1487</v>
+      </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
@@ -10459,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>1309</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10488,7 +11166,10 @@
         <v>585</v>
       </c>
       <c r="I183" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>1503</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
@@ -10519,6 +11200,9 @@
       <c r="I184" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J184" s="3" t="s">
+        <v>1574</v>
+      </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
@@ -10546,10 +11230,10 @@
         <v>642</v>
       </c>
       <c r="I185" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>1291</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
@@ -10580,6 +11264,9 @@
       <c r="I186" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J186" s="3" t="s">
+        <v>1555</v>
+      </c>
     </row>
     <row r="187" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
@@ -10609,6 +11296,9 @@
       <c r="I187" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J187" s="3" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
@@ -10667,6 +11357,9 @@
       <c r="I189" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J189" s="3" t="s">
+        <v>1449</v>
+      </c>
     </row>
     <row r="190" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
@@ -10697,7 +11390,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>1327</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10729,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>1291</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -10760,6 +11453,9 @@
       <c r="I192" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J192" s="3" t="s">
+        <v>1505</v>
+      </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
@@ -10789,6 +11485,9 @@
       <c r="I193" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J193" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
@@ -10819,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>1328</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10848,7 +11547,10 @@
         <v>490</v>
       </c>
       <c r="I195" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>1413</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -10879,6 +11581,9 @@
       <c r="I196" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J196" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
@@ -10906,7 +11611,10 @@
         <v>594</v>
       </c>
       <c r="I197" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
@@ -10966,6 +11674,9 @@
       <c r="I199" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J199" s="3" t="s">
+        <v>1563</v>
+      </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
@@ -10993,7 +11704,10 @@
         <v>110</v>
       </c>
       <c r="I200" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J200" s="3" t="s">
+        <v>1426</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11024,6 +11738,9 @@
       <c r="I201" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J201" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="202" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
@@ -11053,6 +11770,9 @@
       <c r="I202" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J202" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="203" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
@@ -11083,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>1305</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11114,6 +11834,9 @@
       <c r="I204" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J204" s="3" t="s">
+        <v>1564</v>
+      </c>
     </row>
     <row r="205" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
@@ -11141,10 +11864,10 @@
         <v>501</v>
       </c>
       <c r="I205" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1329</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11234,7 +11957,7 @@
         <v>0</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>1291</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11266,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1305</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
@@ -11298,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1309</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11330,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>1330</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11359,10 +12082,10 @@
         <v>55</v>
       </c>
       <c r="I212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>1331</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
@@ -11393,6 +12116,9 @@
       <c r="I213" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J213" s="3" t="s">
+        <v>1426</v>
+      </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
@@ -11422,6 +12148,9 @@
       <c r="I214" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J214" s="3" t="s">
+        <v>1397</v>
+      </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
@@ -11452,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1309</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
@@ -11483,6 +12212,9 @@
       <c r="I216" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J216" s="3" t="s">
+        <v>1508</v>
+      </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
@@ -11542,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>1332</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11573,6 +12305,9 @@
       <c r="I219" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J219" s="3" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="220" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
@@ -11602,6 +12337,9 @@
       <c r="I220" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="J220" s="3" t="s">
+        <v>1562</v>
+      </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
@@ -11631,6 +12369,9 @@
       <c r="I221" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J221" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="222" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
@@ -11661,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>1333</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
@@ -11692,6 +12433,9 @@
       <c r="I223" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J223" s="3" t="s">
+        <v>1563</v>
+      </c>
     </row>
     <row r="224" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
@@ -11721,6 +12465,9 @@
       <c r="I224" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J224" s="9" t="s">
+        <v>1418</v>
+      </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
@@ -11751,7 +12498,7 @@
         <v>0</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>1291</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -11782,6 +12529,9 @@
       <c r="I226" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J226" s="3" t="s">
+        <v>1511</v>
+      </c>
     </row>
     <row r="227" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
@@ -11811,6 +12561,9 @@
       <c r="I227" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J227" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="228" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
@@ -11840,6 +12593,9 @@
       <c r="I228" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J228" s="3" t="s">
+        <v>1453</v>
+      </c>
     </row>
     <row r="229" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
@@ -11870,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="3" t="s">
-        <v>1334</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
@@ -11930,6 +12686,9 @@
       <c r="I231" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J231" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
@@ -11989,7 +12748,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>1305</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
@@ -12020,6 +12779,9 @@
       <c r="I234" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J234" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
@@ -12050,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>1305</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
@@ -12081,6 +12843,9 @@
       <c r="I236" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J236" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
@@ -12111,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>1309</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
@@ -12143,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>1309</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12175,7 +12940,7 @@
         <v>0</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>1335</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
@@ -12235,6 +13000,9 @@
       <c r="I241" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J241" s="3" t="s">
+        <v>1565</v>
+      </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
@@ -12264,6 +13032,9 @@
       <c r="I242" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J242" s="3" t="s">
+        <v>1513</v>
+      </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
@@ -12294,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>1336</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12326,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1309</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
@@ -12358,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>1336</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
@@ -12390,7 +13161,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="3" t="s">
-        <v>1336</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12421,6 +13192,9 @@
       <c r="I247" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J247" s="3" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="248" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
@@ -12450,6 +13224,9 @@
       <c r="I248" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="J248" s="3" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
@@ -12509,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>1337</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
@@ -12538,10 +13315,10 @@
         <v>354</v>
       </c>
       <c r="I251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1305</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12573,7 +13350,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>1338</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12605,7 +13382,7 @@
         <v>1</v>
       </c>
       <c r="J253" s="9" t="s">
-        <v>1339</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
@@ -12637,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="9" t="s">
-        <v>1340</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12669,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="J255" s="9" t="s">
-        <v>1341</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12701,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="J256" s="9" t="s">
-        <v>1342</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12733,7 +13510,7 @@
         <v>1</v>
       </c>
       <c r="J257" s="9" t="s">
-        <v>1343</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12765,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="J258" s="9" t="s">
-        <v>1344</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
@@ -12797,7 +13574,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="9" t="s">
-        <v>1309</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12829,7 +13606,7 @@
         <v>1</v>
       </c>
       <c r="J260" s="9" t="s">
-        <v>1346</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
@@ -12861,7 +13638,7 @@
         <v>1</v>
       </c>
       <c r="J261" s="9" t="s">
-        <v>1347</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12893,7 +13670,7 @@
         <v>1</v>
       </c>
       <c r="J262" s="9" t="s">
-        <v>1347</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -12925,7 +13702,7 @@
         <v>1</v>
       </c>
       <c r="J263" s="9" t="s">
-        <v>1348</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
@@ -12957,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="9" t="s">
-        <v>1349</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
@@ -12988,7 +13765,9 @@
       <c r="I265" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J265" s="9"/>
+      <c r="J265" s="9" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
@@ -13019,7 +13798,7 @@
         <v>1</v>
       </c>
       <c r="J266" s="9" t="s">
-        <v>1350</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
@@ -13048,9 +13827,11 @@
         <v>22</v>
       </c>
       <c r="I267" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J267" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J267" s="9" t="s">
+        <v>1570</v>
+      </c>
     </row>
     <row r="268" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
@@ -13081,7 +13862,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="9" t="s">
-        <v>1351</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
@@ -13113,7 +13894,7 @@
         <v>0</v>
       </c>
       <c r="J269" s="9" t="s">
-        <v>1352</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13145,7 +13926,7 @@
         <v>0</v>
       </c>
       <c r="J270" s="9" t="s">
-        <v>1353</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -13174,10 +13955,10 @@
         <v>830</v>
       </c>
       <c r="I271" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J271" s="9" t="s">
-        <v>1354</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
@@ -13209,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="9" t="s">
-        <v>1355</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
@@ -13240,7 +14021,9 @@
       <c r="I273" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J273" s="9"/>
+      <c r="J273" s="9" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="274" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
@@ -13268,9 +14051,11 @@
         <v>330</v>
       </c>
       <c r="I274" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J274" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J274" s="9" t="s">
+        <v>1555</v>
+      </c>
     </row>
     <row r="275" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
@@ -13301,7 +14086,7 @@
         <v>1</v>
       </c>
       <c r="J275" s="9" t="s">
-        <v>1356</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
@@ -13330,10 +14115,10 @@
         <v>1123</v>
       </c>
       <c r="I276" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="9" t="s">
-        <v>1357</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13365,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="J277" s="9" t="s">
-        <v>1355</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13397,7 +14182,7 @@
         <v>1</v>
       </c>
       <c r="J278" s="9" t="s">
-        <v>1358</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13429,7 +14214,7 @@
         <v>1</v>
       </c>
       <c r="J279" s="9" t="s">
-        <v>1359</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
@@ -13461,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="J280" s="9" t="s">
-        <v>1352</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
@@ -13492,7 +14277,9 @@
       <c r="I281" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J281" s="9"/>
+      <c r="J281" s="9" t="s">
+        <v>1453</v>
+      </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
@@ -13522,7 +14309,9 @@
       <c r="I282" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J282" s="9"/>
+      <c r="J282" s="9" t="s">
+        <v>1519</v>
+      </c>
     </row>
     <row r="283" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
@@ -13550,10 +14339,10 @@
         <v>1067</v>
       </c>
       <c r="I283" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283" s="9" t="s">
-        <v>1360</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -13585,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="J284" s="9" t="s">
-        <v>1359</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13617,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="J285" s="9" t="s">
-        <v>1361</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13649,7 +14438,7 @@
         <v>0</v>
       </c>
       <c r="J286" s="9" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13681,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="J287" s="9" t="s">
-        <v>1363</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13713,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="J288" s="9" t="s">
-        <v>1364</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13745,7 +14534,7 @@
         <v>1</v>
       </c>
       <c r="J289" s="9" t="s">
-        <v>1359</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13777,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="J290" s="9" t="s">
-        <v>1365</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -13809,7 +14598,7 @@
         <v>1</v>
       </c>
       <c r="J291" s="9" t="s">
-        <v>1359</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
@@ -13840,7 +14629,9 @@
       <c r="I292" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J292" s="9"/>
+      <c r="J292" s="9" t="s">
+        <v>1426</v>
+      </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
@@ -13871,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="J293" s="9" t="s">
-        <v>1366</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13900,10 +14691,10 @@
         <v>398</v>
       </c>
       <c r="I294" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" s="9" t="s">
-        <v>1367</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -13935,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="J295" s="9" t="s">
-        <v>1368</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
@@ -13967,7 +14758,7 @@
         <v>0</v>
       </c>
       <c r="J296" s="9" t="s">
-        <v>1369</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
@@ -13996,10 +14787,10 @@
         <v>244</v>
       </c>
       <c r="I297" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J297" s="9" t="s">
-        <v>1370</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14031,7 +14822,7 @@
         <v>1</v>
       </c>
       <c r="J298" s="9" t="s">
-        <v>1371</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14063,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="J299" s="9" t="s">
-        <v>1372</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
@@ -14125,7 +14916,7 @@
         <v>1</v>
       </c>
       <c r="J301" s="9" t="s">
-        <v>1373</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
@@ -14157,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="J302" s="9" t="s">
-        <v>1374</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
@@ -14189,7 +14980,7 @@
         <v>1</v>
       </c>
       <c r="J303" s="9" t="s">
-        <v>1373</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
@@ -14221,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="J304" s="9" t="s">
-        <v>1375</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14283,7 +15074,7 @@
         <v>0</v>
       </c>
       <c r="J306" s="9" t="s">
-        <v>1376</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14312,9 +15103,11 @@
         <v>787</v>
       </c>
       <c r="I307" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J307" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J307" s="9" t="s">
+        <v>1562</v>
+      </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
@@ -14344,8 +15137,8 @@
       <c r="I308" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J308" s="9" t="s">
-        <v>1377</v>
+      <c r="J308" s="3" t="s">
+        <v>1561</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
@@ -14376,7 +15169,9 @@
       <c r="I309" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J309" s="9"/>
+      <c r="J309" s="9" t="s">
+        <v>1565</v>
+      </c>
     </row>
     <row r="310" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
@@ -14406,7 +15201,9 @@
       <c r="I310" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J310" s="9"/>
+      <c r="J310" s="9" t="s">
+        <v>1528</v>
+      </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
@@ -14436,7 +15233,9 @@
       <c r="I311" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J311" s="9"/>
+      <c r="J311" s="9" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="312" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
@@ -14466,7 +15265,9 @@
       <c r="I312" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J312" s="9"/>
+      <c r="J312" s="9" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
@@ -14497,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="J313" s="9" t="s">
-        <v>1378</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
@@ -14529,7 +15330,7 @@
         <v>0</v>
       </c>
       <c r="J314" s="9" t="s">
-        <v>1340</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
@@ -14560,8 +15361,8 @@
       <c r="I315" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="J315" s="9" t="s">
-        <v>1379</v>
+      <c r="J315" s="12" t="s">
+        <v>1566</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14593,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="J316" s="9" t="s">
-        <v>1380</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
@@ -14624,7 +15425,9 @@
       <c r="I317" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J317" s="9"/>
+      <c r="J317" s="9" t="s">
+        <v>1561</v>
+      </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
@@ -14655,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="J318" s="9" t="s">
-        <v>1381</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
@@ -14687,7 +15490,7 @@
         <v>0</v>
       </c>
       <c r="J319" s="9" t="s">
-        <v>1382</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14748,7 +15551,9 @@
       <c r="I321" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J321" s="9"/>
+      <c r="J321" s="9" t="s">
+        <v>1418</v>
+      </c>
     </row>
     <row r="322" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
@@ -14779,7 +15584,7 @@
         <v>0</v>
       </c>
       <c r="J322" s="9" t="s">
-        <v>1340</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14840,7 +15645,9 @@
       <c r="I324" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J324" s="9"/>
+      <c r="J324" s="9" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="325" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
@@ -14871,7 +15678,7 @@
         <v>0</v>
       </c>
       <c r="J325" s="9" t="s">
-        <v>1383</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
@@ -14903,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="J326" s="9" t="s">
-        <v>1381</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14935,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="J327" s="9" t="s">
-        <v>1364</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -14961,12 +15768,14 @@
         <v>497</v>
       </c>
       <c r="H328" s="3" t="s">
-        <v>1313</v>
+        <v>1299</v>
       </c>
       <c r="I328" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J328" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J328" s="9" t="s">
+        <v>1419</v>
+      </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
@@ -14997,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="J329" s="9" t="s">
-        <v>1384</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
@@ -15028,7 +15837,9 @@
       <c r="I330" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J330" s="9"/>
+      <c r="J330" s="9" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="331" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
@@ -15059,7 +15870,7 @@
         <v>0</v>
       </c>
       <c r="J331" s="9" t="s">
-        <v>1385</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
@@ -15091,7 +15902,7 @@
         <v>0</v>
       </c>
       <c r="J332" s="9" t="s">
-        <v>1386</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
@@ -15123,7 +15934,7 @@
         <v>0</v>
       </c>
       <c r="J333" s="9" t="s">
-        <v>1364</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15154,7 +15965,9 @@
       <c r="I334" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="J334" s="9"/>
+      <c r="J334" s="9" t="s">
+        <v>1461</v>
+      </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
@@ -15184,7 +15997,9 @@
       <c r="I335" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="J335" s="9"/>
+      <c r="J335" s="9" t="s">
+        <v>1462</v>
+      </c>
     </row>
     <row r="336" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
@@ -15215,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="J336" s="9" t="s">
-        <v>1387</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15247,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="J337" s="9" t="s">
-        <v>1388</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
@@ -15278,7 +16093,9 @@
       <c r="I338" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J338" s="9"/>
+      <c r="J338" s="9" t="s">
+        <v>1567</v>
+      </c>
     </row>
     <row r="339" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
@@ -15309,7 +16126,7 @@
         <v>1</v>
       </c>
       <c r="J339" s="9" t="s">
-        <v>1389</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
@@ -15341,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="J340" s="9" t="s">
-        <v>1340</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
@@ -15373,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="J341" s="9" t="s">
-        <v>1390</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15405,7 +16222,7 @@
         <v>1</v>
       </c>
       <c r="J342" s="9" t="s">
-        <v>1391</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15436,7 +16253,9 @@
       <c r="I343" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J343" s="9"/>
+      <c r="J343" s="9" t="s">
+        <v>1499</v>
+      </c>
     </row>
     <row r="344" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
@@ -15464,9 +16283,11 @@
         <v>1191</v>
       </c>
       <c r="I344" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J344" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J344" s="9" t="s">
+        <v>1575</v>
+      </c>
     </row>
     <row r="345" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
@@ -15524,10 +16345,10 @@
         <v>648</v>
       </c>
       <c r="I346" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J346" s="9" t="s">
-        <v>1358</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
@@ -15559,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="J347" s="9" t="s">
-        <v>1392</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="348" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15590,7 +16411,9 @@
       <c r="I348" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J348" s="9"/>
+      <c r="J348" s="9" t="s">
+        <v>1519</v>
+      </c>
     </row>
     <row r="349" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
@@ -15621,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="J349" s="9" t="s">
-        <v>1359</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="350" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15653,7 +16476,7 @@
         <v>0</v>
       </c>
       <c r="J350" s="9" t="s">
-        <v>1340</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="351" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -15685,7 +16508,7 @@
         <v>1</v>
       </c>
       <c r="J351" s="9" t="s">
-        <v>1393</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
@@ -15716,7 +16539,9 @@
       <c r="I352" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J352" s="9"/>
+      <c r="J352" s="9" t="s">
+        <v>1563</v>
+      </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
@@ -15746,7 +16571,9 @@
       <c r="I353" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="J353" s="9"/>
+      <c r="J353" s="9" t="s">
+        <v>1398</v>
+      </c>
     </row>
     <row r="354" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
@@ -15776,7 +16603,9 @@
       <c r="I354" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J354" s="9"/>
+      <c r="J354" s="9" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="355" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
@@ -15804,9 +16633,11 @@
         <v>17</v>
       </c>
       <c r="I355" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J355" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J355" s="9" t="s">
+        <v>1289</v>
+      </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
@@ -15867,7 +16698,7 @@
         <v>0</v>
       </c>
       <c r="J357" s="9" t="s">
-        <v>1394</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="358" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -15896,9 +16727,11 @@
         <v>912</v>
       </c>
       <c r="I358" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J358" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J358" s="9" t="s">
+        <v>1420</v>
+      </c>
     </row>
     <row r="359" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
@@ -15929,7 +16762,7 @@
         <v>0</v>
       </c>
       <c r="J359" s="9" t="s">
-        <v>1395</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
@@ -15961,7 +16794,7 @@
         <v>0</v>
       </c>
       <c r="J360" s="9" t="s">
-        <v>1396</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
@@ -15993,7 +16826,7 @@
         <v>0</v>
       </c>
       <c r="J361" s="9" t="s">
-        <v>1364</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
@@ -16025,7 +16858,7 @@
         <v>0</v>
       </c>
       <c r="J362" s="9" t="s">
-        <v>1340</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="363" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16057,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="J363" s="9" t="s">
-        <v>1397</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
@@ -16118,7 +16951,9 @@
       <c r="I365" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J365" s="9"/>
+      <c r="J365" s="9" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
@@ -16149,7 +16984,7 @@
         <v>1</v>
       </c>
       <c r="J366" s="9" t="s">
-        <v>1398</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="367" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16181,7 +17016,7 @@
         <v>1</v>
       </c>
       <c r="J367" s="9" t="s">
-        <v>1399</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="368" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16213,7 +17048,7 @@
         <v>1</v>
       </c>
       <c r="J368" s="9" t="s">
-        <v>1400</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
@@ -16245,7 +17080,7 @@
         <v>0</v>
       </c>
       <c r="J369" s="9" t="s">
-        <v>1401</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="370" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16277,7 +17112,7 @@
         <v>0</v>
       </c>
       <c r="J370" s="9" t="s">
-        <v>1402</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
@@ -16308,7 +17143,9 @@
       <c r="I371" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J371" s="9"/>
+      <c r="J371" s="9" t="s">
+        <v>1567</v>
+      </c>
     </row>
     <row r="372" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
@@ -16338,7 +17175,9 @@
       <c r="I372" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="J372" s="9"/>
+      <c r="J372" s="9" t="s">
+        <v>1464</v>
+      </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
@@ -16369,7 +17208,7 @@
         <v>0</v>
       </c>
       <c r="J373" s="9" t="s">
-        <v>1403</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
@@ -16431,7 +17270,7 @@
         <v>0</v>
       </c>
       <c r="J375" s="9" t="s">
-        <v>1404</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
@@ -16492,7 +17331,9 @@
       <c r="I377" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J377" s="9"/>
+      <c r="J377" s="9" t="s">
+        <v>1539</v>
+      </c>
     </row>
     <row r="378" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
@@ -16523,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="J378" s="9" t="s">
-        <v>1404</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="379" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16552,9 +17393,11 @@
         <v>1223</v>
       </c>
       <c r="I379" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J379" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J379" s="9" t="s">
+        <v>1539</v>
+      </c>
     </row>
     <row r="380" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
@@ -16615,7 +17458,7 @@
         <v>1</v>
       </c>
       <c r="J381" s="10" t="s">
-        <v>1343</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
@@ -16647,7 +17490,7 @@
         <v>0</v>
       </c>
       <c r="J382" s="10" t="s">
-        <v>1405</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
@@ -16678,8 +17521,8 @@
       <c r="I383" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J383" s="10" t="s">
-        <v>1369</v>
+      <c r="J383" s="9" t="s">
+        <v>1458</v>
       </c>
     </row>
     <row r="384" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16711,7 +17554,7 @@
         <v>0</v>
       </c>
       <c r="J384" s="9" t="s">
-        <v>1406</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="385" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16743,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="J385" s="9" t="s">
-        <v>1407</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
@@ -16775,7 +17618,7 @@
         <v>1</v>
       </c>
       <c r="J386" s="9" t="s">
-        <v>1408</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
@@ -16807,7 +17650,7 @@
         <v>1</v>
       </c>
       <c r="J387" s="9" t="s">
-        <v>1409</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="388" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16839,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="J388" s="9" t="s">
-        <v>1410</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="389" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16871,7 +17714,7 @@
         <v>1</v>
       </c>
       <c r="J389" s="9" t="s">
-        <v>1411</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="390" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16903,7 +17746,7 @@
         <v>0</v>
       </c>
       <c r="J390" s="9" t="s">
-        <v>1412</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
@@ -16932,10 +17775,10 @@
         <v>587</v>
       </c>
       <c r="I391" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J391" s="9" t="s">
-        <v>1413</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="392" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -16967,7 +17810,7 @@
         <v>1</v>
       </c>
       <c r="J392" s="9" t="s">
-        <v>1414</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.45">
@@ -16999,7 +17842,7 @@
         <v>1</v>
       </c>
       <c r="J393" s="9" t="s">
-        <v>1415</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="394" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17028,11 +17871,9 @@
         <v>1127</v>
       </c>
       <c r="I394" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J394" s="9" t="s">
-        <v>1416</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J394" s="9"/>
     </row>
     <row r="395" spans="1:10" ht="34" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
@@ -17063,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="J395" s="9" t="s">
-        <v>1417</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.45">
@@ -17092,10 +17933,10 @@
         <v>167</v>
       </c>
       <c r="I396" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" s="9" t="s">
-        <v>1345</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="397" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17127,7 +17968,7 @@
         <v>0</v>
       </c>
       <c r="J397" s="9" t="s">
-        <v>1418</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.45">
@@ -17156,10 +17997,10 @@
         <v>1152</v>
       </c>
       <c r="I398" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J398" s="9" t="s">
-        <v>1345</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="399" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17191,7 +18032,7 @@
         <v>1</v>
       </c>
       <c r="J399" s="9" t="s">
-        <v>1419</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="400" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17223,7 +18064,7 @@
         <v>1</v>
       </c>
       <c r="J400" s="9" t="s">
-        <v>1366</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.45">
@@ -17255,7 +18096,7 @@
         <v>0</v>
       </c>
       <c r="J401" s="9" t="s">
-        <v>1420</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="402" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17287,7 +18128,7 @@
         <v>0</v>
       </c>
       <c r="J402" s="9" t="s">
-        <v>1421</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="403" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17316,10 +18157,10 @@
         <v>648</v>
       </c>
       <c r="I403" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J403" s="9" t="s">
-        <v>1422</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.45">
@@ -17351,7 +18192,7 @@
         <v>0</v>
       </c>
       <c r="J404" s="9" t="s">
-        <v>1423</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.45">
@@ -17383,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="J405" s="9" t="s">
-        <v>1424</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="406" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17415,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="J406" s="9" t="s">
-        <v>1425</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="407" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17447,7 +18288,7 @@
         <v>0</v>
       </c>
       <c r="J407" s="9" t="s">
-        <v>1426</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="408" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -17479,7 +18320,7 @@
         <v>1</v>
       </c>
       <c r="J408" s="9" t="s">
-        <v>1359</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="409" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17508,10 +18349,10 @@
         <v>614</v>
       </c>
       <c r="I409" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J409" s="9" t="s">
-        <v>1427</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.45">
@@ -17543,7 +18384,7 @@
         <v>1</v>
       </c>
       <c r="J410" s="9" t="s">
-        <v>1366</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.45">
@@ -17575,7 +18416,7 @@
         <v>1</v>
       </c>
       <c r="J411" s="9" t="s">
-        <v>1428</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="412" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17607,7 +18448,7 @@
         <v>0</v>
       </c>
       <c r="J412" s="9" t="s">
-        <v>1429</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="413" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17639,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="J413" s="9" t="s">
-        <v>1346</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="414" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17668,10 +18509,10 @@
         <v>894</v>
       </c>
       <c r="I414" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J414" s="9" t="s">
-        <v>1430</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.45">
@@ -17703,7 +18544,7 @@
         <v>1</v>
       </c>
       <c r="J415" s="9" t="s">
-        <v>1431</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="416" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17735,7 +18576,7 @@
         <v>0</v>
       </c>
       <c r="J416" s="9" t="s">
-        <v>1432</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="417" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17767,7 +18608,7 @@
         <v>1</v>
       </c>
       <c r="J417" s="9" t="s">
-        <v>1433</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="418" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17799,7 +18640,7 @@
         <v>1</v>
       </c>
       <c r="J418" s="9" t="s">
-        <v>1434</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.45">
@@ -17831,7 +18672,7 @@
         <v>1</v>
       </c>
       <c r="J419" s="9" t="s">
-        <v>1435</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="420" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17863,7 +18704,7 @@
         <v>1</v>
       </c>
       <c r="J420" s="9" t="s">
-        <v>1343</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="421" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -17895,7 +18736,7 @@
         <v>1</v>
       </c>
       <c r="J421" s="9" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.45">
@@ -17927,7 +18768,7 @@
         <v>0</v>
       </c>
       <c r="J422" s="9" t="s">
-        <v>1437</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.45">
@@ -17959,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="J423" s="9" t="s">
-        <v>1424</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.45">
@@ -17991,7 +18832,7 @@
         <v>1</v>
       </c>
       <c r="J424" s="9" t="s">
-        <v>1438</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="425" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18023,7 +18864,7 @@
         <v>0</v>
       </c>
       <c r="J425" s="9" t="s">
-        <v>1439</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.45">
@@ -18055,7 +18896,7 @@
         <v>1</v>
       </c>
       <c r="J426" s="9" t="s">
-        <v>1440</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="427" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18087,7 +18928,7 @@
         <v>1</v>
       </c>
       <c r="J427" s="9" t="s">
-        <v>1441</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.45">
@@ -18119,7 +18960,7 @@
         <v>0</v>
       </c>
       <c r="J428" s="9" t="s">
-        <v>1410</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.45">
@@ -18151,7 +18992,7 @@
         <v>0</v>
       </c>
       <c r="J429" s="9" t="s">
-        <v>1442</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="430" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18183,7 +19024,7 @@
         <v>0</v>
       </c>
       <c r="J430" s="9" t="s">
-        <v>1443</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.45">
@@ -18215,7 +19056,7 @@
         <v>0</v>
       </c>
       <c r="J431" s="9" t="s">
-        <v>1444</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.45">
@@ -18241,13 +19082,13 @@
         <v>1053</v>
       </c>
       <c r="H432" s="3" t="s">
-        <v>1314</v>
+        <v>1300</v>
       </c>
       <c r="I432" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J432" s="9" t="s">
-        <v>1445</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.45">
@@ -18279,7 +19120,7 @@
         <v>0</v>
       </c>
       <c r="J433" s="9" t="s">
-        <v>1446</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="434" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18311,7 +19152,7 @@
         <v>0</v>
       </c>
       <c r="J434" s="9" t="s">
-        <v>1447</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.45">
@@ -18340,10 +19181,10 @@
         <v>588</v>
       </c>
       <c r="I435" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J435" s="9" t="s">
-        <v>1345</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="436" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18375,7 +19216,7 @@
         <v>1</v>
       </c>
       <c r="J436" s="9" t="s">
-        <v>1448</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="437" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18407,7 +19248,7 @@
         <v>1</v>
       </c>
       <c r="J437" s="9" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.45">
@@ -18439,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="J438" s="9" t="s">
-        <v>1449</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.45">
@@ -18471,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="J439" s="9" t="s">
-        <v>1450</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="440" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18503,7 +19344,7 @@
         <v>0</v>
       </c>
       <c r="J440" s="9" t="s">
-        <v>1375</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="441" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18535,7 +19376,7 @@
         <v>0</v>
       </c>
       <c r="J441" s="9" t="s">
-        <v>1432</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="442" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18567,7 +19408,7 @@
         <v>0</v>
       </c>
       <c r="J442" s="9" t="s">
-        <v>1422</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="443" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18599,7 +19440,7 @@
         <v>0</v>
       </c>
       <c r="J443" s="9" t="s">
-        <v>1439</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="444" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18628,10 +19469,10 @@
         <v>537</v>
       </c>
       <c r="I444" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J444" s="9" t="s">
-        <v>1398</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="445" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18660,10 +19501,10 @@
         <v>620</v>
       </c>
       <c r="I445" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J445" s="9" t="s">
-        <v>1451</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="446" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18695,7 +19536,7 @@
         <v>0</v>
       </c>
       <c r="J446" s="9" t="s">
-        <v>1432</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.45">
@@ -18724,10 +19565,10 @@
         <v>1241</v>
       </c>
       <c r="I447" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J447" s="9" t="s">
-        <v>1431</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.45">
@@ -18759,7 +19600,7 @@
         <v>0</v>
       </c>
       <c r="J448" s="9" t="s">
-        <v>1452</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="449" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18791,7 +19632,7 @@
         <v>1</v>
       </c>
       <c r="J449" s="9" t="s">
-        <v>1453</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="450" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18820,10 +19661,10 @@
         <v>519</v>
       </c>
       <c r="I450" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J450" s="9" t="s">
-        <v>1366</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="451" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -18855,7 +19696,7 @@
         <v>1</v>
       </c>
       <c r="J451" s="9" t="s">
-        <v>1359</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="452" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -18887,7 +19728,7 @@
         <v>1</v>
       </c>
       <c r="J452" s="9" t="s">
-        <v>1454</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="453" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18919,7 +19760,7 @@
         <v>0</v>
       </c>
       <c r="J453" s="9" t="s">
-        <v>1455</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="454" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18951,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="J454" s="9" t="s">
-        <v>1432</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="455" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -18983,7 +19824,7 @@
         <v>1</v>
       </c>
       <c r="J455" s="9" t="s">
-        <v>1435</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="456" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19015,7 +19856,7 @@
         <v>0</v>
       </c>
       <c r="J456" s="9" t="s">
-        <v>1456</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="457" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19047,7 +19888,7 @@
         <v>1</v>
       </c>
       <c r="J457" s="9" t="s">
-        <v>1457</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.45">
@@ -19079,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="J458" s="9" t="s">
-        <v>1458</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="459" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19111,7 +19952,7 @@
         <v>0</v>
       </c>
       <c r="J459" s="9" t="s">
-        <v>1459</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="460" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19143,7 +19984,7 @@
         <v>1</v>
       </c>
       <c r="J460" s="9" t="s">
-        <v>1359</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="461" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19175,7 +20016,7 @@
         <v>0</v>
       </c>
       <c r="J461" s="9" t="s">
-        <v>1460</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="462" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19207,7 +20048,7 @@
         <v>1</v>
       </c>
       <c r="J462" s="9" t="s">
-        <v>1461</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.45">
@@ -19239,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="J463" s="9" t="s">
-        <v>1450</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.45">
@@ -19271,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="J464" s="9" t="s">
-        <v>1435</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.45">
@@ -19303,7 +20144,7 @@
         <v>0</v>
       </c>
       <c r="J465" s="9" t="s">
-        <v>1462</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.45">
@@ -19335,7 +20176,7 @@
         <v>1</v>
       </c>
       <c r="J466" s="9" t="s">
-        <v>1449</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="467" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19367,7 +20208,7 @@
         <v>0</v>
       </c>
       <c r="J467" s="9" t="s">
-        <v>1463</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.45">
@@ -19399,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="J468" s="9" t="s">
-        <v>1464</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.45">
@@ -19431,7 +20272,7 @@
         <v>1</v>
       </c>
       <c r="J469" s="9" t="s">
-        <v>1398</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="470" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19463,7 +20304,7 @@
         <v>1</v>
       </c>
       <c r="J470" s="9" t="s">
-        <v>1400</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="471" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19495,7 +20336,7 @@
         <v>0</v>
       </c>
       <c r="J471" s="9" t="s">
-        <v>1381</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="472" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19527,7 +20368,7 @@
         <v>1</v>
       </c>
       <c r="J472" s="9" t="s">
-        <v>1433</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.45">
@@ -19559,7 +20400,7 @@
         <v>1</v>
       </c>
       <c r="J473" s="9" t="s">
-        <v>1450</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="474" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19591,7 +20432,7 @@
         <v>0</v>
       </c>
       <c r="J474" s="9" t="s">
-        <v>1465</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="475" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19623,7 +20464,7 @@
         <v>0</v>
       </c>
       <c r="J475" s="9" t="s">
-        <v>1466</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.45">
@@ -19655,7 +20496,7 @@
         <v>1</v>
       </c>
       <c r="J476" s="9" t="s">
-        <v>414</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.45">
@@ -19684,10 +20525,10 @@
         <v>1002</v>
       </c>
       <c r="I477" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J477" s="9" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="51" x14ac:dyDescent="0.45">
@@ -19719,7 +20560,7 @@
         <v>1</v>
       </c>
       <c r="J478" s="9" t="s">
-        <v>1468</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19751,7 +20592,7 @@
         <v>0</v>
       </c>
       <c r="J479" s="9" t="s">
-        <v>1469</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="480" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19783,7 +20624,7 @@
         <v>0</v>
       </c>
       <c r="J480" s="9" t="s">
-        <v>1470</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="481" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19812,10 +20653,10 @@
         <v>1129</v>
       </c>
       <c r="I481" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J481" s="9" t="s">
-        <v>1346</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="482" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19847,7 +20688,7 @@
         <v>1</v>
       </c>
       <c r="J482" s="9" t="s">
-        <v>1359</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="483" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19876,10 +20717,10 @@
         <v>1041</v>
       </c>
       <c r="I483" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J483" s="9" t="s">
-        <v>1471</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="484" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19908,10 +20749,10 @@
         <v>149</v>
       </c>
       <c r="I484" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J484" s="9" t="s">
-        <v>1472</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="485" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -19940,10 +20781,10 @@
         <v>533</v>
       </c>
       <c r="I485" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J485" s="9" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.45">
@@ -19975,7 +20816,7 @@
         <v>1</v>
       </c>
       <c r="J486" s="9" t="s">
-        <v>1474</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="487" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20007,7 +20848,7 @@
         <v>1</v>
       </c>
       <c r="J487" s="9" t="s">
-        <v>1475</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.45">
@@ -20039,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="J488" s="9" t="s">
-        <v>1476</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="489" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20071,7 +20912,7 @@
         <v>0</v>
       </c>
       <c r="J489" s="9" t="s">
-        <v>1477</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20103,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="J490" s="9" t="s">
-        <v>1478</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20135,7 +20976,7 @@
         <v>1</v>
       </c>
       <c r="J491" s="9" t="s">
-        <v>1479</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.45">
@@ -20167,7 +21008,7 @@
         <v>0</v>
       </c>
       <c r="J492" s="9" t="s">
-        <v>1480</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.45">
@@ -20199,7 +21040,7 @@
         <v>0</v>
       </c>
       <c r="J493" s="9" t="s">
-        <v>1481</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="494" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20231,7 +21072,7 @@
         <v>0</v>
       </c>
       <c r="J494" s="9" t="s">
-        <v>1482</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="495" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20263,7 +21104,7 @@
         <v>0</v>
       </c>
       <c r="J495" s="9" t="s">
-        <v>1483</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="496" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20292,10 +21133,10 @@
         <v>385</v>
       </c>
       <c r="I496" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J496" s="9" t="s">
-        <v>1435</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="497" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20327,7 +21168,7 @@
         <v>0</v>
       </c>
       <c r="J497" s="9" t="s">
-        <v>1484</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="498" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20359,7 +21200,7 @@
         <v>1</v>
       </c>
       <c r="J498" s="9" t="s">
-        <v>1346</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="499" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20391,7 +21232,7 @@
         <v>0</v>
       </c>
       <c r="J499" s="9" t="s">
-        <v>1485</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="500" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20423,7 +21264,7 @@
         <v>1</v>
       </c>
       <c r="J500" s="9" t="s">
-        <v>1486</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="501" spans="1:10" ht="34" x14ac:dyDescent="0.45">
@@ -20455,11 +21296,11 @@
         <v>1</v>
       </c>
       <c r="J501" s="10" t="s">
-        <v>1487</v>
+        <v>1394</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:J501" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J501">
       <sortCondition descending="1" ref="B1"/>
     </sortState>
